--- a/dados/gerencial/consolidado_gerencial_2023.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2023.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D4" t="n">
         <v>191</v>
       </c>
       <c r="E4" t="n">
-        <v>1584740.49</v>
+        <v>1604635.04</v>
       </c>
       <c r="F4" t="n">
-        <v>1061878.32</v>
+        <v>1048739.77</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44970</v>
+        <v>44965</v>
       </c>
     </row>
     <row r="5">
@@ -516,19 +516,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D5" t="n">
         <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>920825.6899999999</v>
+        <v>936721.0699999999</v>
       </c>
       <c r="F5" t="n">
-        <v>637686.95</v>
+        <v>597850.04</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>44967</v>
+        <v>44970</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>17352.39</v>
+        <v>16344.79</v>
       </c>
       <c r="F6" t="n">
-        <v>10139.62</v>
+        <v>10772.63</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44971</v>
+        <v>44970</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="D7" t="n">
         <v>138</v>
       </c>
       <c r="E7" t="n">
-        <v>1399866.6</v>
+        <v>1412714.68</v>
       </c>
       <c r="F7" t="n">
-        <v>878677.5600000001</v>
+        <v>891597.45</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>44994</v>
+        <v>44993</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D8" t="n">
         <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>924656.6</v>
+        <v>939214.39</v>
       </c>
       <c r="F8" t="n">
-        <v>551464.51</v>
+        <v>564224.14</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>44998</v>
+        <v>44993</v>
       </c>
     </row>
     <row r="9">
@@ -622,10 +622,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13295.5</v>
+        <v>14490.53</v>
       </c>
       <c r="F9" t="n">
-        <v>7973</v>
+        <v>7606.72</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>44998</v>
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
         <v>152</v>
       </c>
       <c r="E10" t="n">
-        <v>1432575.62</v>
+        <v>1434253.29</v>
       </c>
       <c r="F10" t="n">
-        <v>977979.98</v>
+        <v>978608.49</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>45026</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>956272.96</v>
+        <v>897419.14</v>
       </c>
       <c r="F11" t="n">
-        <v>629072.6</v>
+        <v>586900.95</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45026</v>
+        <v>45033</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>14173.56</v>
+        <v>14065.38</v>
       </c>
       <c r="F12" t="n">
-        <v>8179.75</v>
+        <v>7785.52</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45030</v>
+        <v>45026</v>
       </c>
     </row>
     <row r="13">
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
       </c>
       <c r="E13" t="n">
-        <v>1615304.96</v>
+        <v>1511818.21</v>
       </c>
       <c r="F13" t="n">
-        <v>964412</v>
+        <v>972204.53</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45058</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="14">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>946773.36</v>
+        <v>895292.8199999999</v>
       </c>
       <c r="F14" t="n">
-        <v>590029.11</v>
+        <v>590729.92</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45057</v>
+        <v>45056</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>14441.38</v>
+        <v>14588.73</v>
       </c>
       <c r="F15" t="n">
-        <v>8724.91</v>
+        <v>9069.389999999999</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45056</v>
+        <v>45054</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D16" t="n">
         <v>199</v>
       </c>
       <c r="E16" t="n">
-        <v>1572066.9</v>
+        <v>1656429.46</v>
       </c>
       <c r="F16" t="n">
-        <v>1041570.06</v>
+        <v>1051529.88</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45086</v>
+        <v>45089</v>
       </c>
     </row>
     <row r="17">
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D17" t="n">
         <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>1141708.88</v>
+        <v>1068608.54</v>
       </c>
       <c r="F17" t="n">
-        <v>700765.26</v>
+        <v>695828.14</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45086</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>13723.76</v>
+        <v>14427.61</v>
       </c>
       <c r="F18" t="n">
-        <v>8738.73</v>
+        <v>8103.39</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45089</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="19">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D19" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E19" t="n">
-        <v>1634477.68</v>
+        <v>1733069.84</v>
       </c>
       <c r="F19" t="n">
-        <v>1096860.66</v>
+        <v>1101205.99</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45117</v>
+        <v>45124</v>
       </c>
     </row>
     <row r="20">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D20" t="n">
         <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>1157769.36</v>
+        <v>1090207.17</v>
       </c>
       <c r="F20" t="n">
-        <v>695713.79</v>
+        <v>703244.65</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>45119</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>13836.45</v>
+        <v>13955.04</v>
       </c>
       <c r="F21" t="n">
-        <v>8174.25</v>
+        <v>8657.309999999999</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>45117</v>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D22" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E22" t="n">
-        <v>1788508.67</v>
+        <v>1690498.64</v>
       </c>
       <c r="F22" t="n">
-        <v>1216875.52</v>
+        <v>1139263.46</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>45152</v>
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D23" t="n">
         <v>52</v>
       </c>
       <c r="E23" t="n">
-        <v>1164550.19</v>
+        <v>1175237.84</v>
       </c>
       <c r="F23" t="n">
-        <v>801744.26</v>
+        <v>760585.08</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
     </row>
     <row r="24">
@@ -997,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>13858.13</v>
+        <v>13318.7</v>
       </c>
       <c r="F24" t="n">
-        <v>8184.81</v>
+        <v>8169.28</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>45147</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="D25" t="n">
         <v>222</v>
       </c>
       <c r="E25" t="n">
-        <v>1883523.82</v>
+        <v>1890780.42</v>
       </c>
       <c r="F25" t="n">
-        <v>1290039.53</v>
+        <v>1282480.11</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45182</v>
+        <v>45181</v>
       </c>
     </row>
     <row r="26">
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D26" t="n">
         <v>65</v>
       </c>
       <c r="E26" t="n">
-        <v>1350999.88</v>
+        <v>1347583.3</v>
       </c>
       <c r="F26" t="n">
-        <v>877129.9300000001</v>
+        <v>877918.49</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45177</v>
+        <v>45181</v>
       </c>
     </row>
     <row r="27">
@@ -1072,13 +1072,13 @@
         <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>23714.85</v>
+        <v>25343.13</v>
       </c>
       <c r="F27" t="n">
-        <v>16003.82</v>
+        <v>16324.85</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45183</v>
+        <v>45177</v>
       </c>
     </row>
     <row r="28">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D28" t="n">
         <v>220</v>
       </c>
       <c r="E28" t="n">
-        <v>2373868.27</v>
+        <v>2221727.55</v>
       </c>
       <c r="F28" t="n">
-        <v>1497951.1</v>
+        <v>1567513.16</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45209</v>
+        <v>45208</v>
       </c>
     </row>
     <row r="29">
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D29" t="n">
         <v>53</v>
       </c>
       <c r="E29" t="n">
-        <v>1383470.62</v>
+        <v>1454388.91</v>
       </c>
       <c r="F29" t="n">
-        <v>885589.58</v>
+        <v>896758.58</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45211</v>
+        <v>45209</v>
       </c>
     </row>
     <row r="30">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
         <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>59031.9</v>
+        <v>58266.63</v>
       </c>
       <c r="F30" t="n">
-        <v>35333.59</v>
+        <v>35239.21</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45211</v>
+        <v>45208</v>
       </c>
     </row>
     <row r="31">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D31" t="n">
         <v>336</v>
       </c>
       <c r="E31" t="n">
-        <v>2639158.41</v>
+        <v>2474268.79</v>
       </c>
       <c r="F31" t="n">
-        <v>1779145.6</v>
+        <v>1678209.83</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45243</v>
+        <v>45239</v>
       </c>
     </row>
     <row r="32">
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D32" t="n">
         <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>1545424.92</v>
+        <v>1563124.53</v>
       </c>
       <c r="F32" t="n">
-        <v>972056.73</v>
+        <v>968470.96</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>45239</v>
@@ -1222,13 +1222,13 @@
         <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>94391.50999999999</v>
+        <v>99580.32000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>62957.13</v>
+        <v>59302.96</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45243</v>
+        <v>45240</v>
       </c>
     </row>
     <row r="34">
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>619</v>
+        <v>577</v>
       </c>
       <c r="D34" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E34" t="n">
-        <v>3405534.24</v>
+        <v>3200785.92</v>
       </c>
       <c r="F34" t="n">
-        <v>2164555.73</v>
+        <v>2172822.24</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45272</v>
+        <v>45271</v>
       </c>
     </row>
     <row r="35">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="D35" t="n">
         <v>78</v>
       </c>
       <c r="E35" t="n">
-        <v>1652669.34</v>
+        <v>1645534.61</v>
       </c>
       <c r="F35" t="n">
-        <v>1132623.54</v>
+        <v>1137242.83</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45273</v>
+        <v>45271</v>
       </c>
     </row>
     <row r="36">
@@ -1291,19 +1291,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D36" t="n">
         <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>116499.16</v>
+        <v>107674.62</v>
       </c>
       <c r="F36" t="n">
-        <v>70007.60000000001</v>
+        <v>70733.27</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>45271</v>
+        <v>45274</v>
       </c>
     </row>
     <row r="37">
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D37" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E37" t="n">
-        <v>3186515.6</v>
+        <v>3204928.47</v>
       </c>
       <c r="F37" t="n">
-        <v>2149017.92</v>
+        <v>2251770.94</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>45300</v>
@@ -1341,19 +1341,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D38" t="n">
         <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>1708797.93</v>
+        <v>1812115.66</v>
       </c>
       <c r="F38" t="n">
-        <v>1142394.72</v>
+        <v>1131728.61</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>45306</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="39">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D39" t="n">
         <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>103158.44</v>
+        <v>98437.52</v>
       </c>
       <c r="F39" t="n">
-        <v>68885.47</v>
+        <v>65643.50999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45306</v>
+        <v>45303</v>
       </c>
     </row>
     <row r="40">
@@ -1391,10 +1391,10 @@
         <v>3121</v>
       </c>
       <c r="E40" t="n">
-        <v>39867538.02</v>
+        <v>39351851.29</v>
       </c>
       <c r="F40" t="n">
-        <v>26048537.64</v>
+        <v>25954836.28</v>
       </c>
     </row>
   </sheetData>
